--- a/artfynd/A 60047-2020 artfynd.xlsx
+++ b/artfynd/A 60047-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128623240</v>
       </c>
       <c r="B2" t="n">
-        <v>96696</v>
+        <v>96702</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>128623227</v>
       </c>
       <c r="B3" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>128623239</v>
       </c>
       <c r="B4" t="n">
-        <v>80223</v>
+        <v>80227</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>128623232</v>
       </c>
       <c r="B5" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>128623225</v>
       </c>
       <c r="B6" t="n">
-        <v>97454</v>
+        <v>97460</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>128623224</v>
       </c>
       <c r="B7" t="n">
-        <v>80217</v>
+        <v>80221</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>128623230</v>
       </c>
       <c r="B8" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>128623236</v>
       </c>
       <c r="B9" t="n">
-        <v>79083</v>
+        <v>79087</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>128623231</v>
       </c>
       <c r="B10" t="n">
-        <v>80188</v>
+        <v>80192</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 60047-2020 artfynd.xlsx
+++ b/artfynd/A 60047-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128623240</v>
       </c>
       <c r="B2" t="n">
-        <v>96702</v>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>128623225</v>
       </c>
       <c r="B6" t="n">
-        <v>97460</v>
+        <v>97466</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 60047-2020 artfynd.xlsx
+++ b/artfynd/A 60047-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128623240</v>
       </c>
       <c r="B2" t="n">
-        <v>96708</v>
+        <v>96710</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>128623227</v>
       </c>
       <c r="B3" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>128623239</v>
       </c>
       <c r="B4" t="n">
-        <v>80227</v>
+        <v>80229</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>128623232</v>
       </c>
       <c r="B5" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>128623225</v>
       </c>
       <c r="B6" t="n">
-        <v>97466</v>
+        <v>97468</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>128623224</v>
       </c>
       <c r="B7" t="n">
-        <v>80221</v>
+        <v>80223</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>128623230</v>
       </c>
       <c r="B8" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>128623236</v>
       </c>
       <c r="B9" t="n">
-        <v>79087</v>
+        <v>79089</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>128623231</v>
       </c>
       <c r="B10" t="n">
-        <v>80192</v>
+        <v>80194</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 60047-2020 artfynd.xlsx
+++ b/artfynd/A 60047-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128623240</v>
       </c>
       <c r="B2" t="n">
-        <v>96710</v>
+        <v>96711</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>128623225</v>
       </c>
       <c r="B6" t="n">
-        <v>97468</v>
+        <v>97469</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 60047-2020 artfynd.xlsx
+++ b/artfynd/A 60047-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128623240</v>
       </c>
       <c r="B2" t="n">
-        <v>96711</v>
+        <v>96738</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>128623227</v>
       </c>
       <c r="B3" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>128623239</v>
       </c>
       <c r="B4" t="n">
-        <v>80229</v>
+        <v>80256</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>128623232</v>
       </c>
       <c r="B5" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>128623225</v>
       </c>
       <c r="B6" t="n">
-        <v>97469</v>
+        <v>97496</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>128623224</v>
       </c>
       <c r="B7" t="n">
-        <v>80223</v>
+        <v>80250</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>128623230</v>
       </c>
       <c r="B8" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>128623236</v>
       </c>
       <c r="B9" t="n">
-        <v>79089</v>
+        <v>79116</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>128623231</v>
       </c>
       <c r="B10" t="n">
-        <v>80194</v>
+        <v>80221</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 60047-2020 artfynd.xlsx
+++ b/artfynd/A 60047-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128623240</v>
       </c>
       <c r="B2" t="n">
-        <v>96738</v>
+        <v>96744</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>128623227</v>
       </c>
       <c r="B3" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>128623239</v>
       </c>
       <c r="B4" t="n">
-        <v>80256</v>
+        <v>80260</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>128623232</v>
       </c>
       <c r="B5" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>128623225</v>
       </c>
       <c r="B6" t="n">
-        <v>97496</v>
+        <v>97502</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>128623224</v>
       </c>
       <c r="B7" t="n">
-        <v>80250</v>
+        <v>80254</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>128623230</v>
       </c>
       <c r="B8" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>128623236</v>
       </c>
       <c r="B9" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>128623231</v>
       </c>
       <c r="B10" t="n">
-        <v>80221</v>
+        <v>80225</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 60047-2020 artfynd.xlsx
+++ b/artfynd/A 60047-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128623240</v>
       </c>
       <c r="B2" t="n">
-        <v>96744</v>
+        <v>96751</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>128623225</v>
       </c>
       <c r="B6" t="n">
-        <v>97502</v>
+        <v>97509</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 60047-2020 artfynd.xlsx
+++ b/artfynd/A 60047-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128623240</v>
       </c>
       <c r="B2" t="n">
-        <v>96751</v>
+        <v>96755</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>128623227</v>
       </c>
       <c r="B3" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>128623239</v>
       </c>
       <c r="B4" t="n">
-        <v>80260</v>
+        <v>80264</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>128623232</v>
       </c>
       <c r="B5" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>128623225</v>
       </c>
       <c r="B6" t="n">
-        <v>97509</v>
+        <v>97513</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>128623224</v>
       </c>
       <c r="B7" t="n">
-        <v>80254</v>
+        <v>80258</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>128623230</v>
       </c>
       <c r="B8" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>128623236</v>
       </c>
       <c r="B9" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>128623231</v>
       </c>
       <c r="B10" t="n">
-        <v>80225</v>
+        <v>80229</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 60047-2020 artfynd.xlsx
+++ b/artfynd/A 60047-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128623240</v>
       </c>
       <c r="B2" t="n">
-        <v>96755</v>
+        <v>96762</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>128623227</v>
       </c>
       <c r="B3" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>128623239</v>
       </c>
       <c r="B4" t="n">
-        <v>80264</v>
+        <v>80169</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>128623232</v>
       </c>
       <c r="B5" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>128623225</v>
       </c>
       <c r="B6" t="n">
-        <v>97513</v>
+        <v>97520</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>128623224</v>
       </c>
       <c r="B7" t="n">
-        <v>80258</v>
+        <v>80163</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>128623230</v>
       </c>
       <c r="B8" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>128623236</v>
       </c>
       <c r="B9" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>128623231</v>
       </c>
       <c r="B10" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 60047-2020 artfynd.xlsx
+++ b/artfynd/A 60047-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128623240</v>
       </c>
       <c r="B2" t="n">
-        <v>96765</v>
+        <v>96770</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>128623227</v>
       </c>
       <c r="B3" t="n">
-        <v>80134</v>
+        <v>80139</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>128623239</v>
       </c>
       <c r="B4" t="n">
-        <v>80169</v>
+        <v>80174</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>128623232</v>
       </c>
       <c r="B5" t="n">
-        <v>80134</v>
+        <v>80139</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>128623225</v>
       </c>
       <c r="B6" t="n">
-        <v>97523</v>
+        <v>97528</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>128623224</v>
       </c>
       <c r="B7" t="n">
-        <v>80163</v>
+        <v>80168</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>128623230</v>
       </c>
       <c r="B8" t="n">
-        <v>80134</v>
+        <v>80139</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>128623236</v>
       </c>
       <c r="B9" t="n">
-        <v>79029</v>
+        <v>79034</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>128623231</v>
       </c>
       <c r="B10" t="n">
-        <v>80134</v>
+        <v>80139</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 60047-2020 artfynd.xlsx
+++ b/artfynd/A 60047-2020 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128623240</v>
       </c>
       <c r="B2" t="n">
-        <v>96770</v>
+        <v>96778</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
         <v>128623227</v>
       </c>
       <c r="B3" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         <v>128623239</v>
       </c>
       <c r="B4" t="n">
-        <v>80174</v>
+        <v>80175</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -970,7 +970,7 @@
         <v>128623232</v>
       </c>
       <c r="B5" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1067,7 +1067,7 @@
         <v>128623225</v>
       </c>
       <c r="B6" t="n">
-        <v>97528</v>
+        <v>97536</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1164,7 +1164,7 @@
         <v>128623224</v>
       </c>
       <c r="B7" t="n">
-        <v>80168</v>
+        <v>80169</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1261,7 +1261,7 @@
         <v>128623230</v>
       </c>
       <c r="B8" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1358,7 +1358,7 @@
         <v>128623236</v>
       </c>
       <c r="B9" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1455,7 +1455,7 @@
         <v>128623231</v>
       </c>
       <c r="B10" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
